--- a/Receivables Report/archive/Receivables_Report_July_2026_H1.xlsx
+++ b/Receivables Report/archive/Receivables_Report_July_2026_H1.xlsx
@@ -1303,7 +1303,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:14:46</t>
+    <t>2026-07-16 10:03:09</t>
   </si>
   <si>
     <t>Source</t>

--- a/Receivables Report/archive/Receivables_Report_July_2026_H1.xlsx
+++ b/Receivables Report/archive/Receivables_Report_July_2026_H1.xlsx
@@ -1303,7 +1303,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:09</t>
+    <t>2026-07-16 15:22:41</t>
   </si>
   <si>
     <t>Source</t>
